--- a/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10102_顧客詳細取得.xlsx
+++ b/Sample_Project/設計書/B1_顧客管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(Webサービス)_B10102_顧客詳細取得.xlsx
@@ -11781,8 +11781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -11823,8 +11823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -11859,8 +11859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -11897,8 +11897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -11931,8 +11931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -11965,8 +11965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -11999,8 +11999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -12033,8 +12033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -12071,8 +12071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -12105,8 +12105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -12139,8 +12139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -12175,8 +12175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -12209,8 +12209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -12243,8 +12243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -12277,8 +12277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -12315,8 +12315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -12349,8 +12349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -12387,8 +12387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -12421,8 +12421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -12457,8 +12457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -12491,8 +12491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -12525,8 +12525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -12559,8 +12559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -12595,8 +12595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -12629,8 +12629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -12665,8 +12665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -12705,8 +12705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -12739,8 +12739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -12773,8 +12773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -12807,8 +12807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -12859,8 +12859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -12907,8 +12907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -12949,8 +12949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -12983,8 +12983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13017,8 +13017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -13053,8 +13053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -13087,8 +13087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -13121,8 +13121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -13157,8 +13157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -13191,8 +13191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -13227,8 +13227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -13261,8 +13261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -13295,8 +13295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -13329,8 +13329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -13363,8 +13363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -13397,8 +13397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -13433,8 +13433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -13469,8 +13469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -13505,8 +13505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -13543,8 +13543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -13577,8 +13577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -13611,8 +13611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -13645,8 +13645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -13679,8 +13679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -13715,8 +13715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -13749,8 +13749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -13783,8 +13783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -13817,8 +13817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -13851,8 +13851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -13885,8 +13885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -13919,8 +13919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -13953,8 +13953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -13989,8 +13989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14025,8 +14025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -14059,8 +14059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -14093,8 +14093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -14127,8 +14127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -14161,8 +14161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -14201,8 +14201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -14235,8 +14235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -14271,8 +14271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -14307,8 +14307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -14341,8 +14341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -14377,8 +14377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -14413,8 +14413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -14453,8 +14453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -14489,8 +14489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -14525,8 +14525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -14565,8 +14565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -14599,8 +14599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -14635,8 +14635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -14671,8 +14671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -14705,8 +14705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -14741,8 +14741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -14781,8 +14781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -14815,8 +14815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -14849,8 +14849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -14883,8 +14883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -14917,8 +14917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -14953,8 +14953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -14987,8 +14987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15021,8 +15021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -15055,8 +15055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -15089,8 +15089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -15125,8 +15125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -15167,8 +15167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -15207,8 +15207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -15241,8 +15241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -15281,8 +15281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -15321,8 +15321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -15355,8 +15355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -15397,8 +15397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -15433,8 +15433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -15467,8 +15467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -15501,8 +15501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -15537,8 +15537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -15571,8 +15571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -15605,8 +15605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -15639,8 +15639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -15673,8 +15673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -15709,8 +15709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -15743,8 +15743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -15777,8 +15777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -15811,8 +15811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -15845,8 +15845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -15881,8 +15881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -15919,8 +15919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -15959,8 +15959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -15995,8 +15995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16029,8 +16029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -16063,8 +16063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -16105,8 +16105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -16141,8 +16141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -16175,8 +16175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -16209,8 +16209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -16245,8 +16245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -16279,8 +16279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -16317,8 +16317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -16357,8 +16357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -16393,8 +16393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -16429,8 +16429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -16465,8 +16465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -16501,8 +16501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -16537,8 +16537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -16571,8 +16571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -16605,8 +16605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -16639,8 +16639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -16673,8 +16673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -16707,8 +16707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -16745,8 +16745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -16779,8 +16779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -16815,8 +16815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -16849,8 +16849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -16883,8 +16883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -16917,8 +16917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -16951,8 +16951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -16985,8 +16985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17019,8 +17019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17053,8 +17053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17087,8 +17087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -17121,8 +17121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -17155,8 +17155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -17191,8 +17191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -17225,8 +17225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -17259,8 +17259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -17293,8 +17293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -17327,8 +17327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -17361,8 +17361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -17395,8 +17395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -17431,8 +17431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -17465,8 +17465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -17499,8 +17499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -17533,8 +17533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -17567,8 +17567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -17601,8 +17601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -17635,8 +17635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -17669,8 +17669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -17703,8 +17703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -17739,8 +17739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -17775,8 +17775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -17817,8 +17817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -17855,8 +17855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -17893,8 +17893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -17935,8 +17935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -17971,8 +17971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18005,8 +18005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18041,8 +18041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18075,8 +18075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18113,8 +18113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -18153,8 +18153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -18187,8 +18187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -18221,8 +18221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -18255,8 +18255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -18289,8 +18289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -18323,8 +18323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -18357,8 +18357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -18393,8 +18393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -18431,8 +18431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -18465,8 +18465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -18499,8 +18499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -18533,8 +18533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -18567,8 +18567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -18601,8 +18601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -18635,8 +18635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -18669,8 +18669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -18703,8 +18703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -18737,8 +18737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -18771,8 +18771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -18805,8 +18805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -18839,8 +18839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -18877,8 +18877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -18911,8 +18911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -18945,8 +18945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -18979,8 +18979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19013,8 +19013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19047,8 +19047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19081,8 +19081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19115,8 +19115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -19149,8 +19149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -19183,8 +19183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -19217,8 +19217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -19251,8 +19251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -19285,8 +19285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -19319,8 +19319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -19353,8 +19353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -19389,8 +19389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -19423,8 +19423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -19457,8 +19457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -19493,8 +19493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -19529,8 +19529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -19571,8 +19571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -19607,8 +19607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -19641,8 +19641,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -19675,8 +19675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -19709,8 +19709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -19743,8 +19743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -19779,8 +19779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -19813,8 +19813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -19847,8 +19847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -19881,8 +19881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -19915,8 +19915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -19951,8 +19951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -19991,8 +19991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20033,8 +20033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20067,8 +20067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20105,8 +20105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -20139,8 +20139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -20179,8 +20179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -20215,8 +20215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -20251,8 +20251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -20287,8 +20287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -20325,8 +20325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -20359,8 +20359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -20395,8 +20395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -20429,8 +20429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -20463,8 +20463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -20497,8 +20497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -20531,8 +20531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -20565,8 +20565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -20599,8 +20599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -20633,8 +20633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -20667,8 +20667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -20701,8 +20701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -20735,8 +20735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -20771,8 +20771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -20805,8 +20805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -20839,8 +20839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -20873,8 +20873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -20907,8 +20907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -20941,8 +20941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -20977,8 +20977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -21011,8 +21011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -21045,8 +21045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21079,8 +21079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21113,8 +21113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -21147,8 +21147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -21181,8 +21181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -21215,8 +21215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -21251,8 +21251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -21293,8 +21293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -21327,8 +21327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -21361,8 +21361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -21395,8 +21395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -21435,8 +21435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -21471,8 +21471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -21507,8 +21507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -21543,8 +21543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -21581,8 +21581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -21615,8 +21615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -21649,8 +21649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -21683,8 +21683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -21717,8 +21717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -21751,8 +21751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -21785,8 +21785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -21819,8 +21819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -22011,8 +22011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -22053,8 +22053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -22089,8 +22089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -22127,8 +22127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -22161,8 +22161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -22195,8 +22195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -22229,8 +22229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -22263,8 +22263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -22301,8 +22301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -22335,8 +22335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -22369,8 +22369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -22405,8 +22405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -22439,8 +22439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -22473,8 +22473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -22507,8 +22507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -22545,8 +22545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -22579,8 +22579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -22617,8 +22617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -22651,8 +22651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -22687,8 +22687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -22721,8 +22721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -22755,8 +22755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -22789,8 +22789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -22825,8 +22825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -22859,8 +22859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -22895,8 +22895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -22935,8 +22935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -22969,8 +22969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -23003,8 +23003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -23037,8 +23037,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -23075,8 +23075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -23109,8 +23109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -23151,8 +23151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -23185,8 +23185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -23219,8 +23219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -23255,8 +23255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -23289,8 +23289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -23323,8 +23323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -23359,8 +23359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -23393,8 +23393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -23429,8 +23429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -23463,8 +23463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -23497,8 +23497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -23531,8 +23531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -23565,8 +23565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -23599,8 +23599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -23635,8 +23635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -23671,8 +23671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -23707,8 +23707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -23745,8 +23745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -23779,8 +23779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -23813,8 +23813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -23847,8 +23847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -23881,8 +23881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -23917,8 +23917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -23951,8 +23951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -23985,8 +23985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -24019,8 +24019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -24053,8 +24053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -24087,8 +24087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -24121,8 +24121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -24155,8 +24155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -24191,8 +24191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -24227,8 +24227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -24261,8 +24261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -24295,8 +24295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -24329,8 +24329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -24363,8 +24363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -24403,8 +24403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -24437,8 +24437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -24473,8 +24473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -24509,8 +24509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -24543,8 +24543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -24579,8 +24579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -24615,8 +24615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -24655,8 +24655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -24691,8 +24691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -24727,8 +24727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -24767,8 +24767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -24801,8 +24801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -24837,8 +24837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -24873,8 +24873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -24907,8 +24907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -24943,8 +24943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -24983,8 +24983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -25017,8 +25017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -25051,8 +25051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -25085,8 +25085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -25119,8 +25119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -25155,8 +25155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -25189,8 +25189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -25223,8 +25223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -25257,8 +25257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -25291,8 +25291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -25327,8 +25327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -25369,8 +25369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -25409,8 +25409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -25443,8 +25443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -25483,8 +25483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -25523,8 +25523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -25557,8 +25557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -25599,8 +25599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -25635,8 +25635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -25669,8 +25669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -25703,8 +25703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -25739,8 +25739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -25773,8 +25773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -25807,8 +25807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -25841,8 +25841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -25875,8 +25875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -25911,8 +25911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -25945,8 +25945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -25979,8 +25979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -26013,8 +26013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -26047,8 +26047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -26083,8 +26083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -26121,8 +26121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -26161,8 +26161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -26197,8 +26197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -26231,8 +26231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -26265,8 +26265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -26307,8 +26307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -26343,8 +26343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -26377,8 +26377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -26411,8 +26411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -26447,8 +26447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -26481,8 +26481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -26519,8 +26519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -26559,8 +26559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -26595,8 +26595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -26631,8 +26631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -26667,8 +26667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -26703,8 +26703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -26739,8 +26739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -26773,8 +26773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -26807,8 +26807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -26841,8 +26841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -26875,8 +26875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -26909,8 +26909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -26947,8 +26947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -26981,8 +26981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -27017,8 +27017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -27051,8 +27051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -27085,8 +27085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -27119,8 +27119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -27153,8 +27153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -27187,8 +27187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -27221,8 +27221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -27255,8 +27255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -27289,8 +27289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -27323,8 +27323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -27357,8 +27357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -27393,8 +27393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -27427,8 +27427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -27461,8 +27461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -27495,8 +27495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -27529,8 +27529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -27563,8 +27563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -27597,8 +27597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -27633,8 +27633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -27667,8 +27667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -27701,8 +27701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -27735,8 +27735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -27769,8 +27769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -27803,8 +27803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -27837,8 +27837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -27871,8 +27871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -27905,8 +27905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -27941,8 +27941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -27977,8 +27977,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -28019,8 +28019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -28057,8 +28057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -28095,8 +28095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -28137,8 +28137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -28173,8 +28173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -28207,8 +28207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -28243,8 +28243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -28277,8 +28277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -28315,8 +28315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -28355,8 +28355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -28389,8 +28389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -28423,8 +28423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -28457,8 +28457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -28491,8 +28491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -28525,8 +28525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -28559,8 +28559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -28595,8 +28595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -28633,8 +28633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -28667,8 +28667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -28701,8 +28701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -28735,8 +28735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -28769,8 +28769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -28803,8 +28803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -28837,8 +28837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -28871,8 +28871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -28905,8 +28905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -28939,8 +28939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -28973,8 +28973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -29007,8 +29007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -29041,8 +29041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -29079,8 +29079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -29113,8 +29113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -29147,8 +29147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -29181,8 +29181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -29215,8 +29215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -29249,8 +29249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -29283,8 +29283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -29317,8 +29317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -29351,8 +29351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -29385,8 +29385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -29419,8 +29419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -29453,8 +29453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -29487,8 +29487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -29521,8 +29521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -29555,8 +29555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -29591,8 +29591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -29625,8 +29625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -29659,8 +29659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -29695,8 +29695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -29731,8 +29731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -29773,8 +29773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -29809,8 +29809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -29843,8 +29843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -29877,8 +29877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -29911,8 +29911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -29945,8 +29945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -29981,8 +29981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -30015,8 +30015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -30049,8 +30049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -30083,8 +30083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -30117,8 +30117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -30153,8 +30153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -30193,8 +30193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -30235,8 +30235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -30269,8 +30269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -30307,8 +30307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -30341,8 +30341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -30381,8 +30381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -30417,8 +30417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -30453,8 +30453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -30489,8 +30489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -30527,8 +30527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -30561,8 +30561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -30597,8 +30597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -30631,8 +30631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -30665,8 +30665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -30699,8 +30699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -30733,8 +30733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -30767,8 +30767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -30801,8 +30801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -30835,8 +30835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -30869,8 +30869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -30903,8 +30903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -30937,8 +30937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -30973,8 +30973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -31007,8 +31007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -31041,8 +31041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -31075,8 +31075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -31109,8 +31109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -31143,8 +31143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -31179,8 +31179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -31213,8 +31213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -31247,8 +31247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -31281,8 +31281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -31315,8 +31315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -31349,8 +31349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -31383,8 +31383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -31417,8 +31417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -31453,8 +31453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -31495,8 +31495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -31529,8 +31529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -31563,8 +31563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -31597,8 +31597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -31637,8 +31637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -31673,8 +31673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -31709,8 +31709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -31745,8 +31745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -31783,8 +31783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -31817,8 +31817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -31851,8 +31851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -31885,8 +31885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -31919,8 +31919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -31953,8 +31953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -31987,8 +31987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -32021,8 +32021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -32229,8 +32229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -32272,8 +32272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -32309,8 +32309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -32348,8 +32348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -32383,8 +32383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -32418,8 +32418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -32453,8 +32453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -32488,8 +32488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -32527,8 +32527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -32562,8 +32562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -32597,8 +32597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -32634,8 +32634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -32669,8 +32669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -32704,8 +32704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -32739,8 +32739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -32778,8 +32778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -32813,8 +32813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -32852,8 +32852,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -32887,8 +32887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -32924,8 +32924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -32959,8 +32959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -32994,8 +32994,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -33029,8 +33029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -33066,8 +33066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -33101,8 +33101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -33138,8 +33138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -33179,8 +33179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -33214,8 +33214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -33249,8 +33249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -33284,8 +33284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -33323,8 +33323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -33358,8 +33358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -33413,8 +33413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -33462,8 +33462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -33515,8 +33515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -33564,8 +33564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -33621,8 +33621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -33670,8 +33670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-3-1</v>
       </c>
@@ -33705,8 +33705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -33742,8 +33742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -33777,8 +33777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -33812,8 +33812,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -33863,8 +33863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-2-1</v>
       </c>
@@ -33912,8 +33912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -33949,8 +33949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-2-1</v>
       </c>
@@ -33984,8 +33984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-3-1</v>
       </c>
@@ -34019,8 +34019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-4-1</v>
       </c>
@@ -34054,8 +34054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-5-1</v>
       </c>
@@ -34089,8 +34089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-6-1</v>
       </c>
@@ -34124,8 +34124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -34161,8 +34161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -34198,8 +34198,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -34235,8 +34235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -34274,8 +34274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-2-1</v>
       </c>
@@ -34309,8 +34309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-3-1</v>
       </c>
@@ -34344,8 +34344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-4-1</v>
       </c>
@@ -34379,8 +34379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-5-1</v>
       </c>
@@ -34414,8 +34414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -34451,8 +34451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -34486,8 +34486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -34521,8 +34521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -34556,8 +34556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -34591,8 +34591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-6-1</v>
       </c>
@@ -34626,8 +34626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-7-1</v>
       </c>
@@ -34661,8 +34661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-8-1</v>
       </c>
@@ -34696,8 +34696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -34733,8 +34733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -34770,8 +34770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-2-1</v>
       </c>
@@ -34805,8 +34805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-3-1</v>
       </c>
@@ -34840,8 +34840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-4-1</v>
       </c>
@@ -34875,8 +34875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-5-1</v>
       </c>
@@ -34910,8 +34910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -34964,8 +34964,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -35015,8 +35015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -35066,8 +35066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-2</v>
       </c>
@@ -35113,8 +35113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -35150,8 +35150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-2-1</v>
       </c>
@@ -35185,8 +35185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -35222,8 +35222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -35259,8 +35259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -35300,8 +35300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -35337,8 +35337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -35374,8 +35374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -35415,8 +35415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -35450,8 +35450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -35487,8 +35487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -35524,8 +35524,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -35559,8 +35559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -35596,8 +35596,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -35637,8 +35637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-2-1</v>
       </c>
@@ -35672,8 +35672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-3-1</v>
       </c>
@@ -35707,8 +35707,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-4-1</v>
       </c>
@@ -35742,8 +35742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-5-1</v>
       </c>
@@ -35777,8 +35777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -35814,8 +35814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-2-1</v>
       </c>
@@ -35849,8 +35849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-3-1</v>
       </c>
@@ -35884,8 +35884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-4-1</v>
       </c>
@@ -35919,8 +35919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-5-1</v>
       </c>
@@ -35954,8 +35954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -35991,8 +35991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -36034,8 +36034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -36075,8 +36075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -36110,8 +36110,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -36151,8 +36151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -36192,8 +36192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -36227,8 +36227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -36270,8 +36270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -36307,8 +36307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -36342,8 +36342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -36377,8 +36377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -36414,8 +36414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-2-1</v>
       </c>
@@ -36449,8 +36449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-3-1</v>
       </c>
@@ -36484,8 +36484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-4-1</v>
       </c>
@@ -36519,8 +36519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-5-1</v>
       </c>
@@ -36554,8 +36554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -36591,8 +36591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-2-1</v>
       </c>
@@ -36626,8 +36626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-3-1</v>
       </c>
@@ -36661,8 +36661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-4-1</v>
       </c>
@@ -36696,8 +36696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-5-1</v>
       </c>
@@ -36731,8 +36731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -36768,8 +36768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -36807,8 +36807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -36848,8 +36848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -36885,8 +36885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -36920,8 +36920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-3-1</v>
       </c>
@@ -36955,8 +36955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -36998,8 +36998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-2-1</v>
       </c>
@@ -37035,8 +37035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-3-1</v>
       </c>
@@ -37070,8 +37070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-4-1</v>
       </c>
@@ -37105,8 +37105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -37142,8 +37142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-2-1</v>
       </c>
@@ -37177,8 +37177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -37216,8 +37216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -37257,8 +37257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -37294,8 +37294,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -37331,8 +37331,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -37368,8 +37368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -37405,8 +37405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -37442,8 +37442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -37477,8 +37477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -37512,8 +37512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -37547,8 +37547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -37582,8 +37582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -37617,8 +37617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -37656,8 +37656,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -37691,8 +37691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -37728,8 +37728,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -37763,8 +37763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -37798,8 +37798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -37833,8 +37833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -37868,8 +37868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -37903,8 +37903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -37938,8 +37938,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -37973,8 +37973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -38008,8 +38008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-10-1</v>
       </c>
@@ -38043,8 +38043,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-11-1</v>
       </c>
@@ -38078,8 +38078,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -38115,8 +38115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-2-1</v>
       </c>
@@ -38150,8 +38150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-3-1</v>
       </c>
@@ -38185,8 +38185,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-4-1</v>
       </c>
@@ -38220,8 +38220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-5-1</v>
       </c>
@@ -38255,8 +38255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-6-1</v>
       </c>
@@ -38290,8 +38290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-7-1</v>
       </c>
@@ -38325,8 +38325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -38362,8 +38362,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-2-1</v>
       </c>
@@ -38397,8 +38397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-3-1</v>
       </c>
@@ -38432,8 +38432,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-4-1</v>
       </c>
@@ -38467,8 +38467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-5-1</v>
       </c>
@@ -38502,8 +38502,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-6-1</v>
       </c>
@@ -38537,8 +38537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-7-1</v>
       </c>
@@ -38572,8 +38572,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-8-1</v>
       </c>
@@ -38607,8 +38607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-9-1</v>
       </c>
@@ -38642,8 +38642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -38679,8 +38679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -38716,8 +38716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -38759,8 +38759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -38798,8 +38798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -38837,8 +38837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -38880,8 +38880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -38917,8 +38917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-2-1</v>
       </c>
@@ -38952,8 +38952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -38989,8 +38989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -39024,8 +39024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -39063,8 +39063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -39104,8 +39104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -39139,8 +39139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -39174,8 +39174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -39209,8 +39209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -39244,8 +39244,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -39279,8 +39279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -39314,8 +39314,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -39351,8 +39351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -39390,8 +39390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -39425,8 +39425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -39460,8 +39460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-4-1</v>
       </c>
@@ -39495,8 +39495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-5-1</v>
       </c>
@@ -39530,8 +39530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-6-1</v>
       </c>
@@ -39565,8 +39565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-7-1</v>
       </c>
@@ -39600,8 +39600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-8-1</v>
       </c>
@@ -39635,8 +39635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-9-1</v>
       </c>
@@ -39670,8 +39670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-10-1</v>
       </c>
@@ -39705,8 +39705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-11-1</v>
       </c>
@@ -39740,8 +39740,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-12-1</v>
       </c>
@@ -39775,8 +39775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-13-1</v>
       </c>
@@ -39810,8 +39810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -39849,8 +39849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-2-1</v>
       </c>
@@ -39884,8 +39884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-3-1</v>
       </c>
@@ -39919,8 +39919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-4-1</v>
       </c>
@@ -39954,8 +39954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-5-1</v>
       </c>
@@ -39989,8 +39989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-6-1</v>
       </c>
@@ -40024,8 +40024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-7-1</v>
       </c>
@@ -40059,8 +40059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-8-1</v>
       </c>
@@ -40094,8 +40094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-9-1</v>
       </c>
@@ -40129,8 +40129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-10-1</v>
       </c>
@@ -40164,8 +40164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-11-1</v>
       </c>
@@ -40199,8 +40199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-12-1</v>
       </c>
@@ -40234,8 +40234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-13-1</v>
       </c>
@@ -40269,8 +40269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-14-1</v>
       </c>
@@ -40304,8 +40304,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-15-1</v>
       </c>
@@ -40339,8 +40339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -40376,8 +40376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-2-1</v>
       </c>
@@ -40411,8 +40411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-3-1</v>
       </c>
@@ -40446,8 +40446,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -40483,8 +40483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -40520,8 +40520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -40563,8 +40563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -40600,8 +40600,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-2-1</v>
       </c>
@@ -40635,8 +40635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-3-1</v>
       </c>
@@ -40670,8 +40670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-4-1</v>
       </c>
@@ -40705,8 +40705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-5-1</v>
       </c>
@@ -40740,8 +40740,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -40777,8 +40777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-2-1</v>
       </c>
@@ -40812,8 +40812,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-3-1</v>
       </c>
@@ -40847,8 +40847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-4-1</v>
       </c>
@@ -40882,8 +40882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-5-1</v>
       </c>
@@ -40917,8 +40917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -40954,8 +40954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -40995,8 +40995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -41038,8 +41038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-2-1</v>
       </c>
@@ -41073,8 +41073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -41112,8 +41112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-2-1</v>
       </c>
@@ -41147,8 +41147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -41188,8 +41188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -41225,8 +41225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -41262,8 +41262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -41299,8 +41299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -41338,8 +41338,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -41373,8 +41373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -41410,8 +41410,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -41445,8 +41445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -41480,8 +41480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -41515,8 +41515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -41550,8 +41550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -41585,8 +41585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -41620,8 +41620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -41655,8 +41655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-9-1</v>
       </c>
@@ -41690,8 +41690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-10-1</v>
       </c>
@@ -41725,8 +41725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-11-1</v>
       </c>
@@ -41760,8 +41760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -41797,8 +41797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-2-1</v>
       </c>
@@ -41832,8 +41832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-3-1</v>
       </c>
@@ -41867,8 +41867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-4-1</v>
       </c>
@@ -41902,8 +41902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-5-1</v>
       </c>
@@ -41937,8 +41937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-6-1</v>
       </c>
@@ -41972,8 +41972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -42009,8 +42009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -42044,8 +42044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -42079,8 +42079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -42114,8 +42114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-5-1</v>
       </c>
@@ -42149,8 +42149,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-6-1</v>
       </c>
@@ -42184,8 +42184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-7-1</v>
       </c>
@@ -42219,8 +42219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-8-1</v>
       </c>
@@ -42254,8 +42254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -42291,8 +42291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -42334,8 +42334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-2-1</v>
       </c>
@@ -42369,8 +42369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-3-1</v>
       </c>
@@ -42404,8 +42404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-4-1</v>
       </c>
@@ -42439,8 +42439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -42480,8 +42480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -42517,8 +42517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -42554,8 +42554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -42591,8 +42591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -42630,8 +42630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -42665,8 +42665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-3-1</v>
       </c>
@@ -42700,8 +42700,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-4-1</v>
       </c>
@@ -42735,8 +42735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-5-1</v>
       </c>
@@ -42770,8 +42770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-6-1</v>
       </c>
@@ -42805,8 +42805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-7-1</v>
       </c>
@@ -42840,8 +42840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-8-1</v>
       </c>
@@ -42875,8 +42875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-9-1</v>
       </c>
@@ -42910,8 +42910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -42967,8 +42967,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -43020,8 +43020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-2</v>
       </c>
@@ -43067,8 +43067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-3</v>
       </c>
@@ -43114,8 +43114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -43167,8 +43167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -43216,8 +43216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-2</v>
       </c>
@@ -43263,8 +43263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -43298,8 +43298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -43337,8 +43337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -43374,8 +43374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -43427,8 +43427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-2</v>
       </c>
@@ -43474,8 +43474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -43509,8 +43509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -43544,8 +43544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -43579,8 +43579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -43614,8 +43614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -43649,8 +43649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -43684,8 +43684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
